--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -67,6 +67,7 @@
     <sheet name="2026-09-11" sheetId="58" state="visible" r:id="rId58"/>
     <sheet name="2026-09-12" sheetId="59" state="visible" r:id="rId59"/>
     <sheet name="2026-09-13" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="2026-09-14" sheetId="61" state="visible" r:id="rId61"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50265,6 +50266,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-14 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4327</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>14181</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2482</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>27240</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+4467</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>5229</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+429</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>14942</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+2300</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>23200</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+3506</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>8635</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+781</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>26126</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+3262</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Fad</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>2205</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2205</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Hashirama Senju</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>37627</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+4681</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>12862</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>18691</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+4062</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>18693</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1500</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>27676</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2562</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>30587</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+5105</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>10686</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>29303</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3436</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10963</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1106</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4260</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -50290,7 +50290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-14 13:01:00</t>
+          <t>Timestamp: 2026-09-14 13:31:00</t>
         </is>
       </c>
     </row>
@@ -50918,11 +50918,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>37627</v>
+        <v>37677</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+4681</t>
+          <t>+4731</t>
         </is>
       </c>
     </row>
@@ -51053,11 +51053,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>30587</v>
+        <v>30637</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+5105</t>
+          <t>+5155</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -68,6 +68,7 @@
     <sheet name="2026-09-12" sheetId="59" state="visible" r:id="rId59"/>
     <sheet name="2026-09-13" sheetId="60" state="visible" r:id="rId60"/>
     <sheet name="2026-09-14" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="2026-09-15" sheetId="62" state="visible" r:id="rId62"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51145,6 +51146,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-15 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4327</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>14481</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2732</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>29559</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+2319</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>5229</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>15792</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+850</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>693</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+233</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>24142</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+942</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>9285</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+650</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>28358</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+2232</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Fad</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3255</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Hashirama Senju</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>40027</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+2350</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>12862</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>18841</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>19293</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>30051</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2375</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>32361</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1724</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>10686</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>30472</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1169</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>11213</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4260</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -51170,7 +51170,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-15 13:01:00</t>
+          <t>Timestamp: 2026-09-15 13:31:00</t>
         </is>
       </c>
     </row>
@@ -51453,11 +51453,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>29559</v>
+        <v>29609</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+2319</t>
+          <t>+2369</t>
         </is>
       </c>
     </row>
@@ -51738,11 +51738,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>3255</v>
+        <v>3305</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+1050</t>
+          <t>+1100</t>
         </is>
       </c>
     </row>
@@ -51798,11 +51798,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>40027</v>
+        <v>40077</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+2350</t>
+          <t>+2400</t>
         </is>
       </c>
     </row>
@@ -51918,11 +51918,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>30051</v>
+        <v>30101</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2375</t>
+          <t>+2425</t>
         </is>
       </c>
     </row>
@@ -51933,11 +51933,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>32361</v>
+        <v>32411</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+1724</t>
+          <t>+1774</t>
         </is>
       </c>
     </row>
@@ -51963,11 +51963,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>30472</v>
+        <v>30722</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+1169</t>
+          <t>+1419</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -69,6 +69,7 @@
     <sheet name="2026-09-13" sheetId="60" state="visible" r:id="rId60"/>
     <sheet name="2026-09-14" sheetId="61" state="visible" r:id="rId61"/>
     <sheet name="2026-09-15" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="2026-09-16" sheetId="63" state="visible" r:id="rId63"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -52025,6 +52026,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-16 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4327</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>15081</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2732</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>31514</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1905</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>5229</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>16564</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+772</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>993</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>25938</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1796</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>9549</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+264</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>30263</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+1905</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Fad</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>4305</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Wiwokdetok</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>42355</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2278</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>12862</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>19471</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+630</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>20775</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+1482</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>33843</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1432</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>10686</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>31222</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+500</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>11333</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+120</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4260</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -52050,7 +52050,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-16 13:01:00</t>
+          <t>Timestamp: 2026-09-16 13:31:00</t>
         </is>
       </c>
     </row>
@@ -52573,11 +52573,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>30263</v>
+        <v>30363</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+1905</t>
+          <t>+2005</t>
         </is>
       </c>
     </row>
@@ -52693,11 +52693,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>42355</v>
+        <v>42405</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+2278</t>
+          <t>+2328</t>
         </is>
       </c>
     </row>
@@ -52798,11 +52798,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>20775</v>
+        <v>20825</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+1482</t>
+          <t>+1532</t>
         </is>
       </c>
     </row>
@@ -52873,11 +52873,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>11333</v>
+        <v>11583</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+120</t>
+          <t>+370</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -70,6 +70,7 @@
     <sheet name="2026-09-14" sheetId="61" state="visible" r:id="rId61"/>
     <sheet name="2026-09-15" sheetId="62" state="visible" r:id="rId62"/>
     <sheet name="2026-09-16" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="2026-09-17" sheetId="64" state="visible" r:id="rId64"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -52905,6 +52906,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-17 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4327</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>15981</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3282</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+550</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>33321</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1807</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>5229</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>18037</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+1473</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>993</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>27708</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1770</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>9549</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>32123</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+1760</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Fad</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>5242</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+937</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Wiwokdetok</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>44656</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2251</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>12862</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>20071</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>SHINRAIN ZENIN®</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>21325</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+500</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>35511</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1668</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>10686</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>32991</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1769</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>11843</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+260</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4260</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -52930,7 +52930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-17 13:01:00</t>
+          <t>Timestamp: 2026-09-17 13:31:00</t>
         </is>
       </c>
     </row>
@@ -53438,11 +53438,11 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>9549</v>
+        <v>9822</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+273</t>
         </is>
       </c>
     </row>
@@ -53573,11 +53573,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>44656</v>
+        <v>44706</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+2251</t>
+          <t>+2301</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -71,6 +71,7 @@
     <sheet name="2026-09-15" sheetId="62" state="visible" r:id="rId62"/>
     <sheet name="2026-09-16" sheetId="63" state="visible" r:id="rId63"/>
     <sheet name="2026-09-17" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="2026-09-18" sheetId="65" state="visible" r:id="rId65"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53785,6 +53786,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-18 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4327</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>16581</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3783</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+501</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>35577</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+2256</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>5229</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>18969</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+932</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1257</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+264</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>29163</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1455</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>10565</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+743</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>33570</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+1447</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Fad</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>6347</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1105</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Wiwokdetok</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>46975</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2269</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>12862</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>20071</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ryumichel ZENIN ®</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UJKU SHIJAKUT </t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>21325</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>37037</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1526</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>10686</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>34041</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>12389</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+546</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4260</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -53810,7 +53810,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-18 13:01:00</t>
+          <t>Timestamp: 2026-09-18 13:31:00</t>
         </is>
       </c>
     </row>
@@ -53928,11 +53928,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>16581</v>
+        <v>16881</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+600</t>
+          <t>+900</t>
         </is>
       </c>
     </row>
@@ -54333,11 +54333,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>33570</v>
+        <v>33575</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+1447</t>
+          <t>+1452</t>
         </is>
       </c>
     </row>
@@ -54453,11 +54453,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>46975</v>
+        <v>47025</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+2269</t>
+          <t>+2319</t>
         </is>
       </c>
     </row>
@@ -54573,11 +54573,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>37037</v>
+        <v>37067</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+1526</t>
+          <t>+1556</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -72,6 +72,7 @@
     <sheet name="2026-09-16" sheetId="63" state="visible" r:id="rId63"/>
     <sheet name="2026-09-17" sheetId="64" state="visible" r:id="rId64"/>
     <sheet name="2026-09-18" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="2026-09-19" sheetId="66" state="visible" r:id="rId66"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54665,6 +54666,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-19 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MAHORAGA</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4327</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4632</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>17181</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>4113</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+330</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Market | Kokyutosu</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>37219</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+1642</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>5229</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>20119</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1557</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4595</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>30300</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1137</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YinRaku™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>10865</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>35535</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+1960</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>3784</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3898</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Fad</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>7497</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Wiwokdetok</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Floid</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>49375</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+2350</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Suhaib</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>12862</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>20071</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ryumichel ZENIN ®</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>UJKU SHIJAKUT</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>21325</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>39303</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+2236</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>11068</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+382</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>34914</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+873</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>12889</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+500</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4260</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -54690,7 +54690,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-19 13:01:00</t>
+          <t>Timestamp: 2026-09-19 13:31:00</t>
         </is>
       </c>
     </row>
@@ -54909,7 +54909,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Market | Kokyutosu</t>
+          <t>Feeshaib</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -54917,7 +54917,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -55018,11 +55018,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>20119</v>
+        <v>20219</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>+1150</t>
+          <t>+1250</t>
         </is>
       </c>
     </row>
@@ -55333,11 +55333,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>49375</v>
+        <v>49475</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+2350</t>
+          <t>+2450</t>
         </is>
       </c>
     </row>
@@ -55483,11 +55483,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>34914</v>
+        <v>35314</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+873</t>
+          <t>+1273</t>
         </is>
       </c>
     </row>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -73,6 +73,7 @@
     <sheet name="2026-09-17" sheetId="64" state="visible" r:id="rId64"/>
     <sheet name="2026-09-18" sheetId="65" state="visible" r:id="rId65"/>
     <sheet name="2026-09-19" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="2026-09-20" sheetId="67" state="visible" r:id="rId67"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55545,6 +55546,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Sigma Brothers (3223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-20 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>19269</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+19269</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Mahoraga</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>19297</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WoKy</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>29227</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+29227</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GENDERUWO</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>31194</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+26867</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>H U N T E R</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>31246</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+26614</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB ELISEUS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>22768</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+22751</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>INFERNO</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>44623</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+27442</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>GOJU</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9591</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+9591</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>34804</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+30691</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>The prince JI OF NY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>19537</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+19493</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>IcyGhost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>15475</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+15455</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Conrad</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+16384</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Kurumi</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>25954</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+25954</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NPC | Sabrina</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>7926</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Feeshaib</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>25939</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+22662</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>BOBO</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>9236</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+9236</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KataChi</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>26922</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+26922</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Dmtr</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>24870</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+24864</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Scarlet</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>8611</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+8581</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Torune | Anbu</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>59566</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+22347</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>San Pate Té</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>26688</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+21459</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>N O G A R D</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>44799</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+24580</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sabrina Carpenter</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>29341</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+27188</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>HASHIRAMA</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>24981</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+24961</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>BlacKaguya Ô</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>23281</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+23271</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>BEBO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>17009</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+15452</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NPC | SNOOPY</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>23648</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+19053</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S3YL3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>49301</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+19001</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Tipan Tragaleche</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>22771</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+22771</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Mr.Shelby</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>27258</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+27258</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BlacKObito O</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>20836</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+20836</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FEARLESS</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>24238</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+24228</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>™$£iko™°</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>32986</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+22121</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>zDexTerx</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>55605</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+20070</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>SOI</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>21893</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+20663</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Archaic</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>21298</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+17514</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nixervo</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>20344</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+16446</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Fad</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>27467</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+19970</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Abyssteroth</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>18212</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+17932</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Wiwokdetok</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>11261</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+11065</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kojima</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>70621</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+21146</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Uchiha Jamplang</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>33979</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Wampiptipayb.</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>21455</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+21455</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Mabilis labasan</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>17832</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>BlacKenzie O</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>32495</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+12424</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin 2ND</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>15139</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+15139</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ryumichel ZENIN ®</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>10288</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+10288</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>UJKU SHIJAKUT</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>21254</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+21124</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Montag LOBE</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>32993</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+11668</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>a_t_h_a_l_i_a</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>63392</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+24089</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SB | PapiiChan</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>34474</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+23406</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Lite</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>54336</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+19022</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Hound †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>17995</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+17995</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Jorge Sunkaze</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>40216</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+27327</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Haise</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>31435</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+27175</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_3223.xlsx
+++ b/clan_3223.xlsx
@@ -55570,7 +55570,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-20 13:01:00</t>
+          <t>Timestamp: 2026-09-20 13:31:00</t>
         </is>
       </c>
     </row>
